--- a/conference_registration_forms/001_tourism_resilience_council_registration_form--conference_registration_forms.xlsx
+++ b/conference_registration_forms/001_tourism_resilience_council_registration_form--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>do_you_have_a_preferred_currency</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Do you have a preferred currency?</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_language</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Do you have a preferred language?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>attachments</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>country_of_residence</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Country of Residence</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>how_do_you_know_about_this_event</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How did you hear about this event?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_have_for_tourism_activities</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How much time do you have for tourism activities?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What type of tourist experience do you identify with?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1545,414 +1246,6 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>Maybe</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_currency_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>usd</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_currency_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>eur</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_currency_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>gbp</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_currency_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>jpy</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_language_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>english</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_language_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>french</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_language_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>spanish</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>do_you_have_a_preferred_language_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chinese</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>country_of_residence_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>japan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>country_of_residence_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>canada</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>country_of_residence_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>how_do_you_know_about_this_event_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>how_do_you_know_about_this_event_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>word_of_mouth</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Word of Mouth</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>how_do_you_know_about_this_event_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_have_for_tourism_activities_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1-2_days</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1-2 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_have_for_tourism_activities_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2-4_days</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2-4 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_have_for_tourism_activities_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5-7_days</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5-7 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_have_for_tourism_activities_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>more_than_7_days</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>More than 7 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>nature-based</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nature-based</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>culture-based</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Culture-based</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>adventure-based</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Adventure-based</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>food-based</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Food-based</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>relaxation-based</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Relaxation-based</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>what_type_of_tourist_experience_do_you_identify_with_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>education-based</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Education-based</t>
         </is>
       </c>
     </row>
